--- a/feedback_forms/001_digital_care_communication_experience_survey--feedback_forms.xlsx
+++ b/feedback_forms/001_digital_care_communication_experience_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'what_is_the_primary_issue_with_your_recent_visit?',_'value':_''}</t>
+          <t>what_is_the_primary_issue_with_your_recent_visit?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'What is the primary issue with your recent visit?', 'value': ''}</t>
+          <t>What is the primary issue with your recent visit?</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'select_one_of_the_following_options',_'value':_none}</t>
+          <t>select_one_of_the_following_options</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Select one of the following options', 'value': None}</t>
+          <t>Select one of the following options</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'please_choose_at_least_2_from_the_list',_'value':_none}</t>
+          <t>please_choose_at_least_2_from_the_list</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Please choose at least 2 from the list', 'value': None}</t>
+          <t>Please choose at least 2 from the list</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'please_select_one',_'value':_''}</t>
+          <t>please_select_one</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Please select one', 'value': ''}</t>
+          <t>Please select one</t>
         </is>
       </c>
     </row>
